--- a/formulasi_susu_ibu_hamil.xlsx
+++ b/formulasi_susu_ibu_hamil.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/awp/Documents/R-Studio/Praktikum Uji Sensoris/formulasi-fortifikasi-gizi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1EFF66A-BD75-2E4C-85A2-9DB1547CBFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38905076-DAB0-364A-ACBD-A65CB9EB555D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14680" yWindow="660" windowWidth="14720" windowHeight="18460" xr2:uid="{FF84CCF4-5F0C-B242-886F-955B6AC7AF4F}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{FF84CCF4-5F0C-B242-886F-955B6AC7AF4F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">100</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">22</definedName>
     <definedName name="solver_rhs3" localSheetId="0" hidden="1">8</definedName>
-    <definedName name="solver_rhs4" localSheetId="0" hidden="1">1.1</definedName>
+    <definedName name="solver_rhs4" localSheetId="0" hidden="1">11</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">2</definedName>
